--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/TEXAS_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/TEXAS_2018.xlsx
@@ -3109,7 +3109,7 @@
         <v>159</v>
       </c>
       <c r="D153">
-        <v>0.0009392167286904129</v>
+        <v>0.0009392167286904128</v>
       </c>
     </row>
     <row r="154">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C196">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C261">
@@ -5629,7 +5629,7 @@
         <v>161</v>
       </c>
       <c r="D293">
-        <v>0.0009510307755921791</v>
+        <v>0.0009510307755921792</v>
       </c>
     </row>
     <row r="294">
@@ -7825,7 +7825,7 @@
         <v>1608</v>
       </c>
       <c r="D415">
-        <v>0.009498493709020025</v>
+        <v>0.009498493709020023</v>
       </c>
     </row>
     <row r="416">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C425">
@@ -8311,7 +8311,7 @@
         <v>1546</v>
       </c>
       <c r="D442">
-        <v>0.009132258255065273</v>
+        <v>0.009132258255065272</v>
       </c>
     </row>
     <row r="443">
@@ -8365,7 +8365,7 @@
         <v>1604</v>
       </c>
       <c r="D445">
-        <v>0.009474865615216493</v>
+        <v>0.009474865615216491</v>
       </c>
     </row>
     <row r="446">
@@ -9679,7 +9679,7 @@
         <v>163</v>
       </c>
       <c r="D518">
-        <v>0.0009628448224939453</v>
+        <v>0.0009628448224939452</v>
       </c>
     </row>
     <row r="519">
@@ -13081,7 +13081,7 @@
         <v>161</v>
       </c>
       <c r="D707">
-        <v>0.0009510307755921791</v>
+        <v>0.0009510307755921792</v>
       </c>
     </row>
     <row r="708">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C923">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C925">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C926">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1083">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1145">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1152">
@@ -29497,7 +29497,7 @@
         <v>161</v>
       </c>
       <c r="D1619">
-        <v>0.0009510307755921791</v>
+        <v>0.0009510307755921792</v>
       </c>
     </row>
     <row r="1620">
@@ -30109,7 +30109,7 @@
         <v>163</v>
       </c>
       <c r="D1653">
-        <v>0.0009628448224939453</v>
+        <v>0.0009628448224939452</v>
       </c>
     </row>
     <row r="1654">
@@ -31020,7 +31020,7 @@
       </c>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1704">
@@ -36103,7 +36103,7 @@
         <v>155</v>
       </c>
       <c r="D1986">
-        <v>0.0009155886348868805</v>
+        <v>0.0009155886348868804</v>
       </c>
     </row>
     <row r="1987">
